--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T16:33:40+05:30</t>
+    <t>2026-06-11T14:17:09+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,7 +316,7 @@
     <t>DiagnosticReport.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">Meta
+    <t xml:space="preserve">Meta {http://314e.com/fhir/StructureDefinition/meta-314e}
 </t>
   </si>
   <si>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$35</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$61</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1307" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="459">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:17:09+05:30</t>
+    <t>2026-06-18T13:36:33+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1113,23 +1113,361 @@
     <t>DiagnosticReport.presentedForm</t>
   </si>
   <si>
+    <t xml:space="preserve">Attachment
+</t>
+  </si>
+  <si>
+    <t>Entire report as issued</t>
+  </si>
+  <si>
+    <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
+  </si>
+  <si>
+    <t>"application/pdf" is recommended as the most reliable and interoperable in this context.</t>
+  </si>
+  <si>
+    <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:title}
+</t>
+  </si>
+  <si>
+    <t>text (type=ED)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report</t>
+  </si>
+  <si>
+    <t>report</t>
+  </si>
+  <si>
     <t xml:space="preserve">Attachment {http://314e.com/fhir/StructureDefinition/attachment-314e}
 </t>
   </si>
   <si>
-    <t>Entire report as issued</t>
-  </si>
-  <si>
-    <t>Rich text representation of the entire result as issued by the diagnostic service. Multiple formats are allowed but they SHALL be semantically equivalent.</t>
-  </si>
-  <si>
-    <t>"application/pdf" is recommended as the most reliable and interoperable in this context.</t>
-  </si>
-  <si>
-    <t>Gives laboratory the ability to provide its own fully formatted report for clinical fidelity.</t>
-  </si>
-  <si>
-    <t>text (type=ED)</t>
+    <t>DiagnosticReport.presentedForm:report.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.extension</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension:tag</t>
+  </si>
+  <si>
+    <t>tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-tag}
+</t>
+  </si>
+  <si>
+    <t>Semantic categorization tag associated with the attachment</t>
+  </si>
+  <si>
+    <t>A categorization or semantic tag associated with an Attachment.
+This extension allows multiple tags to be associated with an
+Attachment for workflow, classification, indexing, retrieval,
+processing, or application behavior purposes.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.extension:helperFile</t>
+  </si>
+  <si>
+    <t>helperFile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://314e.com/fhir/StructureDefinition/attachment-helperFile}
+</t>
+  </si>
+  <si>
+    <t>Helper file associated with the attachment</t>
+  </si>
+  <si>
+    <t>Provides the path or filename of an auxiliary/helper file required
+for interpretation, transformation, rendering, or processing of
+the attachment content.</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.contentType</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.contentType</t>
+  </si>
+  <si>
+    <t>Mime type of the content, with charset etc.</t>
+  </si>
+  <si>
+    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
+  </si>
+  <si>
+    <t>Processors of the data need to be able to know how to interpret the data.</t>
+  </si>
+  <si>
+    <t>text/plain; charset=UTF-8, image/png</t>
+  </si>
+  <si>
+    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.contentType</t>
+  </si>
+  <si>
+    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
+  </si>
+  <si>
+    <t>./mediaType, ./charset</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.language</t>
+  </si>
+  <si>
+    <t>Human language of the content (BCP-47)</t>
+  </si>
+  <si>
+    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
+  </si>
+  <si>
+    <t>Users need to be able to choose between the languages in a set of attachments.</t>
+  </si>
+  <si>
+    <t>en-AU</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+  </si>
+  <si>
+    <t>Attachment.language</t>
+  </si>
+  <si>
+    <t>./language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base64Binary
+</t>
+  </si>
+  <si>
+    <t>Inline attachment data is prohibited</t>
+  </si>
+  <si>
+    <t>Inline binary data SHALL NOT be populated.
+Attachment content SHALL instead be persisted externally
+and referenced using Attachment.url.</t>
+  </si>
+  <si>
+    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
+  </si>
+  <si>
+    <t>The data needs to able to be transmitted inline.</t>
+  </si>
+  <si>
+    <t>Attachment.data</t>
+  </si>
+  <si>
+    <t>ED.5</t>
+  </si>
+  <si>
+    <t>./data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.url</t>
+  </si>
+  <si>
+    <t xml:space="preserve">url
+</t>
+  </si>
+  <si>
+    <t>Object storage path or external attachment location</t>
+  </si>
+  <si>
+    <t>Reference/path to the externally stored attachment content. Inline binary data in 
+Attachment.data SHALL NOT be populated. Inline content SHALL instead be persisted 
+externally, referenced using this url element, and tagged as 'inline-data-externalized-to-file'.</t>
+  </si>
+  <si>
+    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
+  </si>
+  <si>
+    <t>The data needs to be transmitted by reference.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/logo-small.png</t>
+  </si>
+  <si>
+    <t>Attachment.url</t>
+  </si>
+  <si>
+    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
+  </si>
+  <si>
+    <t>./reference/literal</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.size</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unsignedInt
+</t>
+  </si>
+  <si>
+    <t>Number of bytes of content (if url provided)</t>
+  </si>
+  <si>
+    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
+  </si>
+  <si>
+    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
+  </si>
+  <si>
+    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
+  </si>
+  <si>
+    <t>Attachment.size</t>
+  </si>
+  <si>
+    <t>N/A (needs data type R3 proposal)</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.hash</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.hash</t>
+  </si>
+  <si>
+    <t>Hash of the data (sha-1, base64ed)</t>
+  </si>
+  <si>
+    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
+  </si>
+  <si>
+    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
+  </si>
+  <si>
+    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
+  </si>
+  <si>
+    <t>Attachment.hash</t>
+  </si>
+  <si>
+    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.title</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.title</t>
+  </si>
+  <si>
+    <t>Label to display in place of the data</t>
+  </si>
+  <si>
+    <t>A label or set of text to display in place of the data.</t>
+  </si>
+  <si>
+    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
+  </si>
+  <si>
+    <t>Official Corporate Logo</t>
+  </si>
+  <si>
+    <t>Attachment.title</t>
+  </si>
+  <si>
+    <t>./title/data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:report.creation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm.creation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime {http://314e.com/fhir/ig/StructureDefinition/datetime-314e}
+</t>
+  </si>
+  <si>
+    <t>Date attachment was first created</t>
+  </si>
+  <si>
+    <t>The date that the attachment was first created.</t>
+  </si>
+  <si>
+    <t>This is often tracked as an integrity issue for use of the attachment.</t>
+  </si>
+  <si>
+    <t>Attachment.creation</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Annotation/ notes associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.id</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.contentType</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.language</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.data</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.url</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.size</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.hash</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.title</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
 </sst>
 </file>
@@ -1446,11 +1784,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN35"/>
+  <dimension ref="A1:AN61"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.36328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="35.36328125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="68.87890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
@@ -1468,7 +1806,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.93359375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="31.91796875" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.08984375" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.4296875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.31640625" customWidth="true" bestFit="true"/>
@@ -1477,7 +1815,7 @@
     <col min="26" max="26" width="69.77734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.10546875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.6953125" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="15.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="35.90625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="13.44140625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="11.03515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="30.5546875" customWidth="true" bestFit="true" hidden="true"/>
@@ -5384,7 +5722,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>345</v>
       </c>
@@ -5461,16 +5799,14 @@
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>351</v>
+      </c>
+      <c r="AC35" s="2"/>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>345</v>
@@ -5494,14 +5830,2998 @@
         <v>337</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN35" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C36" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="D36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="P36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN36" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="37" hidden="true">
+      <c r="A37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN37" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" hidden="true">
+      <c r="A38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN38" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="D39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="40" hidden="true">
+      <c r="A40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="B40" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="D40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E40" s="2"/>
+      <c r="F40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G40" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K40" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M40" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q40" s="2"/>
+      <c r="R40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF40" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG40" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH40" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ40" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM40" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN40" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="41" hidden="true">
+      <c r="A41" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C41" s="2"/>
+      <c r="D41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E41" s="2"/>
+      <c r="F41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J41" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K41" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L41" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M41" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N41" s="2"/>
+      <c r="O41" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q41" s="2"/>
+      <c r="R41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T41" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="U41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X41" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y41" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z41" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF41" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG41" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH41" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ41" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM41" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN41" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="42" hidden="true">
+      <c r="A42" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="B42" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C42" s="2"/>
+      <c r="D42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E42" s="2"/>
+      <c r="F42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K42" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L42" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N42" s="2"/>
+      <c r="O42" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q42" s="2"/>
+      <c r="R42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T42" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="U42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X42" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z42" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF42" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG42" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH42" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ42" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM42" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN42" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="43" hidden="true">
+      <c r="A43" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C43" s="2"/>
+      <c r="D43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E43" s="2"/>
+      <c r="F43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K43" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L43" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M43" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N43" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O43" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="P43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q43" s="2"/>
+      <c r="R43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF43" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG43" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH43" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ43" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK43" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM43" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN43" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="44" hidden="true">
+      <c r="A44" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="B44" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C44" s="2"/>
+      <c r="D44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E44" s="2"/>
+      <c r="F44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K44" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L44" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M44" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q44" s="2"/>
+      <c r="R44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T44" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="U44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF44" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG44" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH44" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ44" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK44" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM44" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN44" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" hidden="true">
+      <c r="A45" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="B45" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C45" s="2"/>
+      <c r="D45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E45" s="2"/>
+      <c r="F45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L45" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="O45" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="P45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q45" s="2"/>
+      <c r="R45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF45" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG45" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH45" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ45" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM45" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN45" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" hidden="true">
+      <c r="A46" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="B46" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C46" s="2"/>
+      <c r="D46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E46" s="2"/>
+      <c r="F46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J46" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K46" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L46" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M46" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N46" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q46" s="2"/>
+      <c r="R46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF46" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG46" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH46" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ46" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" hidden="true">
+      <c r="A47" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="B47" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C47" s="2"/>
+      <c r="D47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E47" s="2"/>
+      <c r="F47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J47" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K47" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q47" s="2"/>
+      <c r="R47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S47" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="T47" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="U47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF47" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG47" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH47" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM47" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN47" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="48" hidden="true">
+      <c r="A48" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="B48" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C48" s="2"/>
+      <c r="D48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E48" s="2"/>
+      <c r="F48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J48" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K48" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L48" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q48" s="2"/>
+      <c r="R48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF48" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG48" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH48" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ48" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL48" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN48" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C49" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="D49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E49" s="2"/>
+      <c r="F49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H49" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K49" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="L49" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>348</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="P49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q49" s="2"/>
+      <c r="R49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF49" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="AG49" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH49" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ49" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL49" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="N51" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="O51" s="2"/>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AN51" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" hidden="true">
+      <c r="A52" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="B52" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C52" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="D52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K52" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="L52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q52" s="2"/>
+      <c r="R52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF52" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG52" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH52" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM52" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN52" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53" hidden="true">
+      <c r="A53" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B53" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="C53" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="D53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E53" s="2"/>
+      <c r="F53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K53" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L53" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M53" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q53" s="2"/>
+      <c r="R53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF53" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AG53" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH53" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ53" t="s" s="2">
+        <v>140</v>
+      </c>
+      <c r="AK53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM53" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AN53" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="54" hidden="true">
+      <c r="A54" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B54" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C54" s="2"/>
+      <c r="D54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E54" s="2"/>
+      <c r="F54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K54" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L54" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="M54" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="N54" s="2"/>
+      <c r="O54" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="P54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q54" s="2"/>
+      <c r="R54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T54" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="U54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X54" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="Y54" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="Z54" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AA54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF54" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG54" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH54" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ54" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK54" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AM54" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AN54" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B55" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C55" s="2"/>
+      <c r="D55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E55" s="2"/>
+      <c r="F55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K55" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="L55" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="N55" s="2"/>
+      <c r="O55" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="P55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q55" s="2"/>
+      <c r="R55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T55" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="U55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X55" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="Y55" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="Z55" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AA55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF55" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AG55" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH55" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM55" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AN55" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" hidden="true">
+      <c r="A56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B56" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C56" s="2"/>
+      <c r="D56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E56" s="2"/>
+      <c r="F56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="H56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="K56" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L56" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M56" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N56" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O56" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="P56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q56" s="2"/>
+      <c r="R56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF56" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG56" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH56" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ56" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK56" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AN56" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="57" hidden="true">
+      <c r="A57" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="B57" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="C57" s="2"/>
+      <c r="D57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E57" s="2"/>
+      <c r="F57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J57" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K57" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="L57" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M57" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="O57" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="P57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T57" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="U57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF57" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AG57" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH57" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ57" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AM57" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="AN57" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="58" hidden="true">
+      <c r="A58" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="B58" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="C58" s="2"/>
+      <c r="D58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E58" s="2"/>
+      <c r="F58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J58" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K58" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="L58" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="N58" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="O58" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="P58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AG58" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH58" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ58" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN58" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="B59" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="C59" s="2"/>
+      <c r="D59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E59" s="2"/>
+      <c r="F59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J59" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K59" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="L59" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M59" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N59" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O59" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="P59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF59" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AG59" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH59" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ59" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM59" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN59" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" hidden="true">
+      <c r="A60" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="B60" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="C60" s="2"/>
+      <c r="D60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E60" s="2"/>
+      <c r="F60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="G60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J60" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K60" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M60" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N60" s="2"/>
+      <c r="O60" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="P60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S60" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="T60" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="U60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF60" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="AG60" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH60" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM60" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="AN60" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="61" hidden="true">
+      <c r="A61" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="B61" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C61" s="2"/>
+      <c r="D61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E61" s="2"/>
+      <c r="F61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J61" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K61" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="L61" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="M61" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="N61" s="2"/>
+      <c r="O61" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="P61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF61" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AG61" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH61" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ61" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN35">
+  <autoFilter ref="A1:AN61">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -5511,7 +8831,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI34">
+  <conditionalFormatting sqref="A2:AI60">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2252" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="448">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T13:36:33+05:30</t>
+    <t>2026-06-18T14:15:04+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1146,13 +1146,22 @@
 </t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.id</t>
+    <t>DiagnosticReport.presentedForm:notes</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>Annotation/ notes associated with the diagnostic report</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.presentedForm:notes.id</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.id</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension</t>
+    <t>DiagnosticReport.presentedForm:notes.extension</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.extension</t>
@@ -1161,7 +1170,7 @@
     <t>Extensions are always sliced by (at least) url</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension:tag</t>
+    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
   </si>
   <si>
     <t>tag</t>
@@ -1180,7 +1189,7 @@
 processing, or application behavior purposes.</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.extension:helperFile</t>
+    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
   </si>
   <si>
     <t>helperFile</t>
@@ -1198,7 +1207,7 @@
 the attachment content.</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.contentType</t>
+    <t>DiagnosticReport.presentedForm:notes.contentType</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.contentType</t>
@@ -1231,7 +1240,7 @@
     <t>./mediaType, ./charset</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.language</t>
+    <t>DiagnosticReport.presentedForm:notes.language</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.language</t>
@@ -1258,7 +1267,7 @@
     <t>./language</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.data</t>
+    <t>DiagnosticReport.presentedForm:notes.data</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.data</t>
@@ -1291,7 +1300,7 @@
     <t>./data</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.url</t>
+    <t>DiagnosticReport.presentedForm:notes.url</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.url</t>
@@ -1327,7 +1336,7 @@
     <t>./reference/literal</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.size</t>
+    <t>DiagnosticReport.presentedForm:notes.size</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.size</t>
@@ -1355,7 +1364,7 @@
     <t>N/A (needs data type R3 proposal)</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.hash</t>
+    <t>DiagnosticReport.presentedForm:notes.hash</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.hash</t>
@@ -1379,7 +1388,7 @@
     <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.title</t>
+    <t>DiagnosticReport.presentedForm:notes.title</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.title</t>
@@ -1394,6 +1403,9 @@
     <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
   </si>
   <si>
+    <t>Note</t>
+  </si>
+  <si>
     <t>Official Corporate Logo</t>
   </si>
   <si>
@@ -1403,7 +1415,7 @@
     <t>./title/data</t>
   </si>
   <si>
-    <t>DiagnosticReport.presentedForm:report.creation</t>
+    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm.creation</t>
@@ -1423,51 +1435,6 @@
   </si>
   <si>
     <t>Attachment.creation</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes</t>
-  </si>
-  <si>
-    <t>notes</t>
-  </si>
-  <si>
-    <t>Annotation/ notes associated with the diagnostic report</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.id</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension:tag</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.extension:helperFile</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.contentType</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.language</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.data</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.url</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.size</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.hash</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.title</t>
-  </si>
-  <si>
-    <t>DiagnosticReport.presentedForm:notes.creation</t>
   </si>
 </sst>
 </file>
@@ -1784,10 +1751,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN61"/>
+  <dimension ref="A1:AN49"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.06640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="68.87890625" customWidth="true" bestFit="true" hidden="true"/>
@@ -5954,14 +5921,16 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" hidden="true">
+    <row r="37">
       <c r="A37" t="s" s="2">
         <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="C37" t="s" s="2">
         <v>357</v>
       </c>
-      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5970,10 +5939,10 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H37" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I37" t="s" s="2">
         <v>20</v>
@@ -5982,16 +5951,20 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>307</v>
+        <v>355</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>358</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N37" s="2"/>
-      <c r="O37" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="O37" t="s" s="2">
+        <v>350</v>
+      </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
       </c>
@@ -6039,28 +6012,28 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>310</v>
+        <v>345</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>20</v>
+        <v>337</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6068,21 +6041,21 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>20</v>
@@ -6094,17 +6067,15 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>134</v>
+        <v>307</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>309</v>
+      </c>
+      <c r="N38" s="2"/>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6141,31 +6112,31 @@
         <v>20</v>
       </c>
       <c r="AB38" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AC38" t="s" s="2">
-        <v>360</v>
+        <v>20</v>
       </c>
       <c r="AD38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
@@ -6185,13 +6156,11 @@
         <v>361</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C39" t="s" s="2">
         <v>362</v>
       </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -6210,15 +6179,17 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>363</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>313</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>314</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6255,16 +6226,16 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>20</v>
+        <v>363</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>315</v>
@@ -6288,7 +6259,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>20</v>
+        <v>311</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6296,13 +6267,13 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C40" t="s" s="2">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D40" t="s" s="2">
         <v>20</v>
@@ -6312,7 +6283,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6324,13 +6295,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="L40" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6410,12 +6381,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C41" s="2"/>
+        <v>362</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>370</v>
+      </c>
       <c r="D41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6433,21 +6406,19 @@
         <v>20</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>109</v>
+        <v>371</v>
       </c>
       <c r="L41" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="M41" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="M41" t="s" s="2">
-        <v>374</v>
-      </c>
       <c r="N41" s="2"/>
-      <c r="O41" t="s" s="2">
-        <v>375</v>
-      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
       </c>
@@ -6459,7 +6430,7 @@
         <v>20</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>376</v>
+        <v>20</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>20</v>
@@ -6471,13 +6442,13 @@
         <v>20</v>
       </c>
       <c r="X41" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="Y41" t="s" s="2">
-        <v>377</v>
+        <v>20</v>
       </c>
       <c r="Z41" t="s" s="2">
-        <v>378</v>
+        <v>20</v>
       </c>
       <c r="AA41" t="s" s="2">
         <v>20</v>
@@ -6495,28 +6466,28 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>379</v>
+        <v>315</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6524,10 +6495,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6553,14 +6524,14 @@
         <v>109</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6573,7 +6544,7 @@
         <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>20</v>
@@ -6585,13 +6556,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>114</v>
+        <v>380</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6609,7 +6580,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6627,10 +6598,10 @@
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>20</v>
+        <v>383</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6638,10 +6609,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6652,7 +6623,7 @@
         <v>78</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>20</v>
@@ -6661,22 +6632,20 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>393</v>
+        <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N43" t="s" s="2">
-        <v>396</v>
-      </c>
+        <v>388</v>
+      </c>
+      <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6689,7 +6658,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>20</v>
+        <v>390</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -6701,13 +6670,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>20</v>
+        <v>391</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6725,7 +6694,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6743,10 +6712,10 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>399</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>400</v>
+        <v>393</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6754,10 +6723,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>401</v>
+        <v>394</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>402</v>
+        <v>395</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6765,10 +6734,10 @@
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6777,22 +6746,22 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>403</v>
+        <v>396</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>404</v>
+        <v>397</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>405</v>
+        <v>398</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>406</v>
+        <v>399</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>407</v>
+        <v>400</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6805,7 +6774,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>408</v>
+        <v>20</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -6841,7 +6810,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6859,10 +6828,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6870,10 +6839,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6881,7 +6850,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>89</v>
@@ -6896,19 +6865,19 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6921,7 +6890,7 @@
         <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>20</v>
+        <v>411</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>20</v>
@@ -6957,7 +6926,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>419</v>
+        <v>412</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6975,10 +6944,10 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>20</v>
+        <v>413</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -6986,10 +6955,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7012,19 +6981,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>393</v>
+        <v>417</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7073,7 +7042,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7094,7 +7063,7 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7102,10 +7071,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7113,7 +7082,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -7128,17 +7097,19 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>307</v>
+        <v>396</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>427</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>428</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7148,10 +7119,10 @@
         <v>20</v>
       </c>
       <c r="S47" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>434</v>
+        <v>20</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -7187,7 +7158,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7208,7 +7179,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7216,10 +7187,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7227,7 +7198,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7242,17 +7213,17 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>439</v>
+        <v>307</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>441</v>
+        <v>435</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>442</v>
+        <v>436</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7262,10 +7233,10 @@
         <v>20</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>20</v>
+        <v>437</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>20</v>
+        <v>438</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>20</v>
@@ -7301,7 +7272,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7322,22 +7293,20 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C49" t="s" s="2">
-        <v>445</v>
-      </c>
+        <v>442</v>
+      </c>
+      <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>20</v>
       </c>
@@ -7346,31 +7315,29 @@
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I49" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J49" t="s" s="2">
         <v>90</v>
       </c>
-      <c r="I49" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J49" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="K49" t="s" s="2">
-        <v>355</v>
+        <v>443</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N49" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O49" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7419,13 +7386,13 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>345</v>
+        <v>447</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>20</v>
@@ -7437,1391 +7404,17 @@
         <v>20</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>352</v>
+        <v>423</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="50" hidden="true">
-      <c r="A50" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="C50" s="2"/>
-      <c r="D50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E50" s="2"/>
-      <c r="F50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K50" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="M50" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q50" s="2"/>
-      <c r="R50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="AG50" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH50" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL50" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM50" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" hidden="true">
-      <c r="A51" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="B51" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C51" s="2"/>
-      <c r="D51" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="E51" s="2"/>
-      <c r="F51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O51" s="2"/>
-      <c r="P51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q51" s="2"/>
-      <c r="R51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>137</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG51" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH51" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ51" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL51" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM51" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="52" hidden="true">
-      <c r="A52" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="B52" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C52" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="D52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E52" s="2"/>
-      <c r="F52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>364</v>
-      </c>
-      <c r="M52" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="N52" s="2"/>
-      <c r="O52" s="2"/>
-      <c r="P52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q52" s="2"/>
-      <c r="R52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF52" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG52" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH52" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ52" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" hidden="true">
-      <c r="A53" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="B53" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="C53" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="D53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E53" s="2"/>
-      <c r="F53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M53" t="s" s="2">
-        <v>370</v>
-      </c>
-      <c r="N53" s="2"/>
-      <c r="O53" s="2"/>
-      <c r="P53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q53" s="2"/>
-      <c r="R53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AG53" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH53" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ53" t="s" s="2">
-        <v>140</v>
-      </c>
-      <c r="AK53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AN53" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" hidden="true">
-      <c r="A54" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="B54" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C54" s="2"/>
-      <c r="D54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E54" s="2"/>
-      <c r="F54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J54" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K54" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L54" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="M54" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="P54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q54" s="2"/>
-      <c r="R54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T54" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="U54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X54" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="Y54" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="Z54" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AA54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF54" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="AG54" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH54" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ54" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK54" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL54" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AN54" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" hidden="true">
-      <c r="A55" t="s" s="2">
-        <v>452</v>
-      </c>
-      <c r="B55" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="C55" s="2"/>
-      <c r="D55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E55" s="2"/>
-      <c r="F55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J55" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K55" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="L55" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="N55" s="2"/>
-      <c r="O55" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="P55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q55" s="2"/>
-      <c r="R55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T55" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="U55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X55" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="Y55" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="Z55" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="AA55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF55" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AG55" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH55" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ55" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL55" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM55" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="56" hidden="true">
-      <c r="A56" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="B56" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="C56" s="2"/>
-      <c r="D56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E56" s="2"/>
-      <c r="F56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="H56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="K56" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="L56" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O56" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q56" s="2"/>
-      <c r="R56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AG56" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH56" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ56" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK56" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" hidden="true">
-      <c r="A57" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="B57" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="C57" s="2"/>
-      <c r="D57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E57" s="2"/>
-      <c r="F57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J57" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K57" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="P57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T57" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="U57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF57" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AG57" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH57" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ57" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK57" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL57" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" hidden="true">
-      <c r="A58" t="s" s="2">
-        <v>455</v>
-      </c>
-      <c r="B58" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="C58" s="2"/>
-      <c r="D58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E58" s="2"/>
-      <c r="F58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J58" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K58" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="P58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF58" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="AG58" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH58" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ58" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AN58" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" hidden="true">
-      <c r="A59" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="C59" s="2"/>
-      <c r="D59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E59" s="2"/>
-      <c r="F59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J59" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K59" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="M59" t="s" s="2">
-        <v>424</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="P59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF59" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="AG59" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH59" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ59" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL59" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" hidden="true">
-      <c r="A60" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="C60" s="2"/>
-      <c r="D60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E60" s="2"/>
-      <c r="F60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="G60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J60" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K60" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="M60" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N60" s="2"/>
-      <c r="O60" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="P60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S60" t="s" s="2">
-        <v>446</v>
-      </c>
-      <c r="T60" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="U60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="AG60" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH60" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ60" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>436</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" hidden="true">
-      <c r="A61" t="s" s="2">
-        <v>458</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>438</v>
-      </c>
-      <c r="C61" s="2"/>
-      <c r="D61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="E61" s="2"/>
-      <c r="F61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="H61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="I61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="J61" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="K61" t="s" s="2">
-        <v>439</v>
-      </c>
-      <c r="L61" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>441</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" t="s" s="2">
-        <v>442</v>
-      </c>
-      <c r="P61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Y61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Z61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF61" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="AG61" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH61" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ61" t="s" s="2">
-        <v>101</v>
-      </c>
-      <c r="AK61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>420</v>
-      </c>
-      <c r="AN61" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN61">
+  <autoFilter ref="A1:AN49">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8831,7 +7424,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI60">
+  <conditionalFormatting sqref="A2:AI48">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1817" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="453">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T14:15:04+05:30</t>
+    <t>2026-06-18T16:14:31+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -660,6 +660,22 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-category</t>
+  </si>
+  <si>
+    <t>DiagnosticReport.category:subCategory</t>
+  </si>
+  <si>
+    <t>subCategory</t>
+  </si>
+  <si>
+    <t>Optional detailed subcategory</t>
+  </si>
+  <si>
+    <t>More granular operational sub-classification of the
+diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-subcategory-314e</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -1751,7 +1767,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN49"/>
+  <dimension ref="A1:AN50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
@@ -3630,15 +3646,17 @@
         <v>204</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>204</v>
-      </c>
-      <c r="C17" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C17" t="s" s="2">
+        <v>205</v>
+      </c>
       <c r="D17" t="s" s="2">
-        <v>205</v>
+        <v>187</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3662,7 +3680,7 @@
         <v>207</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -3688,13 +3706,11 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="Y17" t="s" s="2">
-        <v>210</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y17" s="2"/>
       <c r="Z17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3712,13 +3728,13 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
@@ -3727,28 +3743,28 @@
         <v>101</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>212</v>
+        <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>215</v>
+        <v>198</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -3767,18 +3783,18 @@
         <v>90</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>220</v>
-      </c>
-      <c r="N18" s="2"/>
-      <c r="O18" t="s" s="2">
-        <v>221</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>20</v>
       </c>
@@ -3802,13 +3818,13 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>20</v>
+        <v>214</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>20</v>
+        <v>215</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>20</v>
+        <v>216</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3826,10 +3842,10 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>89</v>
@@ -3841,32 +3857,32 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>225</v>
+        <v>220</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G19" t="s" s="2">
         <v>89</v>
@@ -3881,19 +3897,17 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>225</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -3942,7 +3956,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3957,28 +3971,28 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>236</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
@@ -3997,19 +4011,19 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4058,7 +4072,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4067,34 +4081,34 @@
         <v>89</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>244</v>
+        <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4113,19 +4127,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4174,7 +4188,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4183,41 +4197,41 @@
         <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>20</v>
+        <v>249</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>250</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>258</v>
+        <v>253</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>90</v>
@@ -4229,19 +4243,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4290,13 +4304,13 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
@@ -4305,28 +4319,28 @@
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>266</v>
+        <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -4336,7 +4350,7 @@
         <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -4345,19 +4359,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4406,7 +4420,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4421,28 +4435,28 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4458,22 +4472,22 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="N24" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="O24" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4522,7 +4536,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4537,28 +4551,28 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>20</v>
+        <v>271</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>224</v>
+        <v>273</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>20</v>
+        <v>274</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>285</v>
+        <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4568,7 +4582,7 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
@@ -4577,19 +4591,19 @@
         <v>20</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>287</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>289</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>290</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4638,7 +4652,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4656,25 +4670,25 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>292</v>
+        <v>229</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>20</v>
+        <v>290</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4684,7 +4698,7 @@
         <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4693,18 +4707,20 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>294</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="M26" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>20</v>
       </c>
@@ -4752,7 +4768,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4770,25 +4786,25 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>20</v>
+        <v>296</v>
       </c>
       <c r="AM26" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AN26" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AN26" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>299</v>
-      </c>
       <c r="B27" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>300</v>
+        <v>20</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4798,27 +4814,27 @@
         <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M27" t="s" s="2">
         <v>301</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N27" s="2"/>
-      <c r="O27" t="s" s="2">
-        <v>304</v>
-      </c>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4866,7 +4882,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4884,53 +4900,55 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="AN27" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>20</v>
+        <v>305</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="L28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="M28" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M28" t="s" s="2">
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
         <v>309</v>
       </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4978,28 +4996,28 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK28" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL28" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="AG28" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH28" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK28" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL28" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AM28" t="s" s="2">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
@@ -5007,21 +5025,21 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>20</v>
@@ -5033,7 +5051,7 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="L29" t="s" s="2">
         <v>313</v>
@@ -5041,9 +5059,7 @@
       <c r="M29" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N29" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5098,13 +5114,13 @@
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>20</v>
@@ -5113,7 +5129,7 @@
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5121,14 +5137,14 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>317</v>
+        <v>148</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5141,10 +5157,10 @@
         <v>20</v>
       </c>
       <c r="I30" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
         <v>134</v>
@@ -5158,9 +5174,7 @@
       <c r="N30" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O30" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
       </c>
@@ -5229,7 +5243,7 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>132</v>
+        <v>316</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5244,38 +5258,38 @@
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>20</v>
+        <v>322</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>307</v>
+        <v>134</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>324</v>
+        <v>151</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>325</v>
+        <v>152</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -5324,19 +5338,19 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK31" t="s" s="2">
         <v>20</v>
@@ -5345,18 +5359,18 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN31" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" hidden="true">
+      <c r="A32" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AN31" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="2">
-        <v>327</v>
-      </c>
       <c r="B32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5364,31 +5378,35 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H32" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>328</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>329</v>
       </c>
-      <c r="M32" t="s" s="2">
+      <c r="O32" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="N32" s="2"/>
-      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>20</v>
       </c>
@@ -5436,10 +5454,10 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>89</v>
@@ -5463,7 +5481,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
         <v>332</v>
       </c>
@@ -5472,26 +5490,26 @@
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>333</v>
+        <v>20</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>334</v>
@@ -5500,9 +5518,7 @@
         <v>335</v>
       </c>
       <c r="N33" s="2"/>
-      <c r="O33" t="s" s="2">
-        <v>336</v>
-      </c>
+      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5553,7 +5569,7 @@
         <v>332</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -5568,10 +5584,10 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>337</v>
+        <v>20</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>20</v>
@@ -5579,21 +5595,21 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>20</v>
+        <v>338</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>20</v>
@@ -5605,16 +5621,18 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>188</v>
+        <v>312</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" s="2"/>
+      <c r="O34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="N34" s="2"/>
-      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5638,13 +5656,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5662,13 +5680,13 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>20</v>
@@ -5680,10 +5698,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5691,10 +5709,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5708,7 +5726,7 @@
         <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s" s="2">
         <v>20</v>
@@ -5717,20 +5735,16 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="L35" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O35" t="s" s="2">
-        <v>350</v>
-      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5754,29 +5768,31 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>20</v>
+        <v>348</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="AC35" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5794,25 +5810,23 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C36" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5833,19 +5847,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N36" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O36" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -5882,19 +5896,17 @@
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC36" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="AC36" s="2"/>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5912,10 +5924,10 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
@@ -5923,13 +5935,13 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C37" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D37" t="s" s="2">
         <v>20</v>
@@ -5951,19 +5963,19 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>350</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6012,7 +6024,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6030,23 +6042,25 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="38" hidden="true">
+    <row r="38">
       <c r="A38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>360</v>
-      </c>
-      <c r="C38" s="2"/>
+        <v>350</v>
+      </c>
+      <c r="C38" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6055,10 +6069,10 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>20</v>
@@ -6067,16 +6081,20 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>307</v>
+        <v>360</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>308</v>
+        <v>363</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>309</v>
-      </c>
-      <c r="N38" s="2"/>
-      <c r="O38" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="O38" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
       </c>
@@ -6124,28 +6142,28 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>20</v>
+        <v>342</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>311</v>
+        <v>357</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
@@ -6153,21 +6171,21 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>20</v>
@@ -6179,7 +6197,7 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>134</v>
+        <v>312</v>
       </c>
       <c r="L39" t="s" s="2">
         <v>313</v>
@@ -6187,9 +6205,7 @@
       <c r="M39" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N39" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -6226,16 +6242,16 @@
         <v>20</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>363</v>
+        <v>20</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>315</v>
@@ -6244,13 +6260,13 @@
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
@@ -6259,7 +6275,7 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6267,16 +6283,14 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="C40" t="s" s="2">
-        <v>365</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
@@ -6295,15 +6309,17 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>366</v>
+        <v>134</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>367</v>
+        <v>318</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>319</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6340,19 +6356,19 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>20</v>
+        <v>368</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6373,7 +6389,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>20</v>
+        <v>316</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6384,7 +6400,7 @@
         <v>369</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="C41" t="s" s="2">
         <v>370</v>
@@ -6397,7 +6413,7 @@
         <v>78</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>20</v>
@@ -6466,7 +6482,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6498,9 +6514,11 @@
         <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="C42" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6518,21 +6536,19 @@
         <v>20</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>109</v>
+        <v>376</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N42" s="2"/>
-      <c r="O42" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>20</v>
       </c>
@@ -6544,7 +6560,7 @@
         <v>20</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>379</v>
+        <v>20</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>20</v>
@@ -6556,13 +6572,13 @@
         <v>20</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="Y42" t="s" s="2">
-        <v>380</v>
+        <v>20</v>
       </c>
       <c r="Z42" t="s" s="2">
-        <v>381</v>
+        <v>20</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>20</v>
@@ -6580,28 +6596,28 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>382</v>
+        <v>320</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>383</v>
+        <v>20</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>20</v>
@@ -6609,10 +6625,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>385</v>
+        <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>386</v>
+        <v>380</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6638,14 +6654,14 @@
         <v>109</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>387</v>
+        <v>381</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>388</v>
+        <v>382</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>389</v>
+        <v>383</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>20</v>
@@ -6658,7 +6674,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -6670,13 +6686,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>114</v>
+        <v>385</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>391</v>
+        <v>386</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6694,7 +6710,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6712,10 +6728,10 @@
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>20</v>
+        <v>388</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6723,10 +6739,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6737,7 +6753,7 @@
         <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>20</v>
@@ -6746,22 +6762,20 @@
         <v>20</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>396</v>
+        <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>399</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6774,7 +6788,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>20</v>
+        <v>395</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -6786,13 +6800,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>20</v>
+        <v>396</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6810,7 +6824,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6828,10 +6842,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>402</v>
+        <v>20</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6839,10 +6853,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6850,10 +6864,10 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6862,22 +6876,22 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6890,7 +6904,7 @@
         <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>411</v>
+        <v>20</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>20</v>
@@ -6926,7 +6940,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>412</v>
+        <v>406</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6944,10 +6958,10 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>414</v>
+        <v>408</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -6955,10 +6969,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>409</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>416</v>
+        <v>410</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6966,7 +6980,7 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G46" t="s" s="2">
         <v>89</v>
@@ -6981,19 +6995,19 @@
         <v>90</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7006,7 +7020,7 @@
         <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>20</v>
+        <v>416</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>20</v>
@@ -7042,7 +7056,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7060,10 +7074,10 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>20</v>
+        <v>418</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7071,10 +7085,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7097,19 +7111,19 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="M47" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="O47" t="s" s="2">
         <v>426</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>427</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7158,7 +7172,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7179,7 +7193,7 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7187,10 +7201,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7198,7 +7212,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>89</v>
@@ -7213,17 +7227,19 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>307</v>
+        <v>401</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="N48" s="2"/>
-      <c r="O48" t="s" s="2">
-        <v>436</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7233,10 +7249,10 @@
         <v>20</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>437</v>
+        <v>20</v>
       </c>
       <c r="T48" t="s" s="2">
-        <v>438</v>
+        <v>20</v>
       </c>
       <c r="U48" t="s" s="2">
         <v>20</v>
@@ -7272,7 +7288,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7293,7 +7309,7 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7301,10 +7317,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7312,7 +7328,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7327,17 +7343,17 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>443</v>
+        <v>312</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7347,10 +7363,10 @@
         <v>20</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>20</v>
+        <v>442</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>20</v>
+        <v>443</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>20</v>
@@ -7386,7 +7402,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7407,14 +7423,128 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>423</v>
+        <v>445</v>
       </c>
       <c r="AN49" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="P50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN49">
+  <autoFilter ref="A1:AN50">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7424,7 +7554,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$51</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1853" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1889" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T16:14:31+05:30</t>
+    <t>2026-06-24T16:34:23+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -546,7 +546,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/careplan-314e|http://314e.com/fhir/StructureDefinition/immunizationrecommendation-314e|http://314e.com/fhir/StructureDefinition/medicationrequest-314e|http://314e.com/fhir/StructureDefinition/nutritionorder-314e|http://314e.com/fhir/StructureDefinition/servicerequest-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -662,6 +662,22 @@
     <t>http://hl7.org/fhir/us/core/ValueSet/us-core-diagnosticreport-category</t>
   </si>
   <si>
+    <t>DiagnosticReport.category:broadCategory</t>
+  </si>
+  <si>
+    <t>broadCategory</t>
+  </si>
+  <si>
+    <t>Required broad procedure/service category</t>
+  </si>
+  <si>
+    <t>Top-level operational classification of the
+diagnostic report.</t>
+  </si>
+  <si>
+    <t>http://314e.com/fhir/ValueSet/procedure-category-broad-314e</t>
+  </si>
+  <si>
     <t>DiagnosticReport.category:subCategory</t>
   </si>
   <si>
@@ -722,7 +738,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-patient) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/patient-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -754,7 +770,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-encounter) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/encounter-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -860,7 +876,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-practitioner|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-organization) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/organization-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -895,7 +911,7 @@
 Reported by</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/practitioner-314e|http://314e.com/fhir/StructureDefinition/practitionerrole-314e|http://314e.com/fhir/StructureDefinition/organization-314e|http://314e.com/fhir/StructureDefinition/careteam-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -914,7 +930,7 @@
     <t>DiagnosticReport.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/specimen-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -940,7 +956,7 @@
 Atomic ValueResultAtomic resultDataTestAnalyteBatteryOrganizer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-observation-lab|http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-observation-clinical-result) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/observation-lab-general-314e|http://314e.com/fhir/StructureDefinition/observation-microbiology-314e|http://314e.com/fhir/StructureDefinition/observation-microorganism-314e|http://314e.com/fhir/StructureDefinition/observation-antimicrobial-susceptibility-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -965,7 +981,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.org/fhir/us/qicore/StructureDefinition/qicore-imagingstudy) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/imagingstudy-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1073,7 +1089,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media) {http://314e.com/fhir/StructureDefinition/reference-314e}
+    <t xml:space="preserve">Reference(http://314e.com/fhir/StructureDefinition/media-314e) {http://314e.com/fhir/StructureDefinition/reference-314e}
 </t>
   </si>
   <si>
@@ -1767,12 +1783,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN50"/>
+  <dimension ref="A1:AN51"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.46484375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="38.25390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.16796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="12.8671875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="68.87890625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.29296875" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.21484375" customWidth="true" bestFit="true"/>
@@ -1780,7 +1796,7 @@
     <col min="8" max="8" width="13.1171875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.75390625" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="183.66796875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3656,7 +3672,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>89</v>
@@ -3760,15 +3776,17 @@
         <v>209</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>210</v>
+      </c>
       <c r="D18" t="s" s="2">
-        <v>210</v>
+        <v>187</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>89</v>
@@ -3792,7 +3810,7 @@
         <v>212</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>213</v>
+        <v>191</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3818,13 +3836,11 @@
         <v>20</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>215</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="Y18" s="2"/>
       <c r="Z18" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>20</v>
@@ -3842,13 +3858,13 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>209</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
@@ -3857,28 +3873,28 @@
         <v>101</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>217</v>
+        <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>218</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>219</v>
+        <v>197</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>220</v>
+        <v>198</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3897,18 +3913,18 @@
         <v>90</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>223</v>
+        <v>188</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" t="s" s="2">
-        <v>226</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="N19" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>20</v>
       </c>
@@ -3932,13 +3948,13 @@
         <v>20</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>20</v>
+        <v>219</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>20</v>
+        <v>220</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>20</v>
+        <v>221</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>20</v>
@@ -3956,10 +3972,10 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>89</v>
@@ -3971,32 +3987,32 @@
         <v>101</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>225</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>89</v>
@@ -4011,19 +4027,17 @@
         <v>90</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>236</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" t="s" s="2">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>20</v>
@@ -4072,7 +4086,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4087,28 +4101,28 @@
         <v>101</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>241</v>
+        <v>235</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
@@ -4127,19 +4141,19 @@
         <v>90</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -4188,7 +4202,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4197,34 +4211,34 @@
         <v>89</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>249</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
@@ -4243,19 +4257,19 @@
         <v>90</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
@@ -4304,7 +4318,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4313,41 +4327,41 @@
         <v>89</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>20</v>
+        <v>254</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>101</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>20</v>
+        <v>255</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>263</v>
+        <v>258</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>90</v>
@@ -4359,19 +4373,19 @@
         <v>90</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4420,13 +4434,13 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
@@ -4435,28 +4449,28 @@
         <v>101</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>271</v>
+        <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>274</v>
+        <v>268</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -4466,7 +4480,7 @@
         <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>20</v>
@@ -4475,19 +4489,19 @@
         <v>90</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
@@ -4536,7 +4550,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4551,28 +4565,28 @@
         <v>101</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>20</v>
+        <v>281</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4588,22 +4602,22 @@
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>283</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="N25" t="s" s="2">
-        <v>286</v>
-      </c>
       <c r="O25" t="s" s="2">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4652,7 +4666,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4667,28 +4681,28 @@
         <v>101</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>20</v>
+        <v>276</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>229</v>
+        <v>278</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>20</v>
+        <v>279</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>290</v>
+        <v>20</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4698,7 +4712,7 @@
         <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I26" t="s" s="2">
         <v>20</v>
@@ -4707,19 +4721,19 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -4768,7 +4782,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4786,25 +4800,25 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>297</v>
+        <v>234</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4814,7 +4828,7 @@
         <v>79</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
@@ -4823,18 +4837,20 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="N27" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M27" t="s" s="2">
-        <v>301</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>20</v>
       </c>
@@ -4882,7 +4898,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4900,25 +4916,25 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>20</v>
+        <v>301</v>
       </c>
       <c r="AM27" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
         <v>303</v>
       </c>
-      <c r="AN27" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>304</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>305</v>
+        <v>20</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -4928,27 +4944,27 @@
         <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" t="s" s="2">
-        <v>309</v>
-      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>20</v>
       </c>
@@ -4996,7 +5012,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5014,53 +5030,55 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>310</v>
+        <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>20</v>
+        <v>310</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J29" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>312</v>
       </c>
-      <c r="L29" t="s" s="2">
+      <c r="M29" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="M29" t="s" s="2">
+      <c r="N29" s="2"/>
+      <c r="O29" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="N29" s="2"/>
-      <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>20</v>
       </c>
@@ -5108,28 +5126,28 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK29" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL29" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="AG29" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH29" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AI29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AJ29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AK29" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>20</v>
-      </c>
       <c r="AM29" t="s" s="2">
-        <v>316</v>
+        <v>302</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>20</v>
@@ -5137,21 +5155,21 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>20</v>
@@ -5163,7 +5181,7 @@
         <v>20</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>134</v>
+        <v>317</v>
       </c>
       <c r="L30" t="s" s="2">
         <v>318</v>
@@ -5171,9 +5189,7 @@
       <c r="M30" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N30" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5228,13 +5244,13 @@
         <v>78</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>20</v>
@@ -5243,7 +5259,7 @@
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>20</v>
@@ -5251,14 +5267,14 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>322</v>
+        <v>148</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -5271,10 +5287,10 @@
         <v>20</v>
       </c>
       <c r="I31" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
         <v>134</v>
@@ -5288,9 +5304,7 @@
       <c r="N31" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="O31" t="s" s="2">
-        <v>152</v>
-      </c>
+      <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>20</v>
       </c>
@@ -5359,7 +5373,7 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>132</v>
+        <v>321</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>20</v>
@@ -5374,38 +5388,38 @@
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>20</v>
+        <v>327</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>312</v>
+        <v>134</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>329</v>
+        <v>151</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>330</v>
+        <v>152</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5454,19 +5468,19 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>20</v>
@@ -5475,18 +5489,18 @@
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="AN32" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" hidden="true">
+      <c r="A33" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AN32" t="s" s="2">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>332</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5494,31 +5508,35 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G33" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>334</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="N33" s="2"/>
-      <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>20</v>
       </c>
@@ -5566,10 +5584,10 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="AG33" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="AH33" t="s" s="2">
         <v>89</v>
@@ -5593,7 +5611,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
         <v>337</v>
       </c>
@@ -5602,26 +5620,26 @@
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>338</v>
+        <v>20</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G34" t="s" s="2">
         <v>89</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>312</v>
+        <v>338</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>339</v>
@@ -5630,9 +5648,7 @@
         <v>340</v>
       </c>
       <c r="N34" s="2"/>
-      <c r="O34" t="s" s="2">
-        <v>341</v>
-      </c>
+      <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>20</v>
       </c>
@@ -5683,7 +5699,7 @@
         <v>337</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="AH34" t="s" s="2">
         <v>89</v>
@@ -5698,10 +5714,10 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>342</v>
+        <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>20</v>
@@ -5709,21 +5725,21 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>20</v>
+        <v>343</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>20</v>
@@ -5735,16 +5751,18 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>188</v>
+        <v>317</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="M35" t="s" s="2">
+      <c r="N35" s="2"/>
+      <c r="O35" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>20</v>
       </c>
@@ -5768,13 +5786,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>192</v>
+        <v>20</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>347</v>
+        <v>20</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>348</v>
+        <v>20</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -5792,13 +5810,13 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>20</v>
@@ -5810,10 +5828,10 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="AN35" t="s" s="2">
         <v>20</v>
@@ -5821,10 +5839,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5838,7 +5856,7 @@
         <v>79</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>20</v>
@@ -5847,20 +5865,16 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="L36" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O36" t="s" s="2">
-        <v>355</v>
-      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>20</v>
       </c>
@@ -5884,29 +5898,31 @@
         <v>20</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>20</v>
+        <v>192</v>
       </c>
       <c r="Y36" t="s" s="2">
-        <v>20</v>
+        <v>352</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>20</v>
+        <v>353</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>356</v>
-      </c>
-      <c r="AC36" s="2"/>
+        <v>20</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>20</v>
+      </c>
       <c r="AD36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5924,25 +5940,23 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="C37" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>355</v>
+      </c>
+      <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>20</v>
       </c>
@@ -5963,19 +5977,19 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O37" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L37" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6012,19 +6026,17 @@
         <v>20</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>20</v>
-      </c>
+        <v>361</v>
+      </c>
+      <c r="AC37" s="2"/>
       <c r="AD37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6042,10 +6054,10 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>20</v>
@@ -6053,13 +6065,13 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>20</v>
@@ -6081,19 +6093,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O38" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>363</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>355</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6142,7 +6154,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6160,23 +6172,25 @@
         <v>20</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="C39" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="C39" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="D39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6185,10 +6199,10 @@
         <v>78</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H39" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="I39" t="s" s="2">
         <v>20</v>
@@ -6197,16 +6211,20 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>312</v>
+        <v>365</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>313</v>
+        <v>368</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+        <v>358</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O39" t="s" s="2">
+        <v>360</v>
+      </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
       </c>
@@ -6254,28 +6272,28 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>315</v>
+        <v>355</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>20</v>
+        <v>101</v>
       </c>
       <c r="AK39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>316</v>
+        <v>362</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>20</v>
@@ -6283,21 +6301,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>20</v>
@@ -6309,7 +6327,7 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>134</v>
+        <v>317</v>
       </c>
       <c r="L40" t="s" s="2">
         <v>318</v>
@@ -6317,9 +6335,7 @@
       <c r="M40" t="s" s="2">
         <v>319</v>
       </c>
-      <c r="N40" t="s" s="2">
-        <v>151</v>
-      </c>
+      <c r="N40" s="2"/>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -6356,16 +6372,16 @@
         <v>20</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>368</v>
+        <v>20</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>138</v>
+        <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>320</v>
@@ -6374,13 +6390,13 @@
         <v>78</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>20</v>
@@ -6389,7 +6405,7 @@
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>20</v>
@@ -6397,16 +6413,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="C41" t="s" s="2">
-        <v>370</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>20</v>
+        <v>148</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6425,15 +6439,17 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>371</v>
+        <v>134</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>372</v>
+        <v>323</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="N41" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N41" t="s" s="2">
+        <v>151</v>
+      </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6470,19 +6486,19 @@
         <v>20</v>
       </c>
       <c r="AB41" t="s" s="2">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="AC41" t="s" s="2">
-        <v>20</v>
+        <v>373</v>
       </c>
       <c r="AD41" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>20</v>
+        <v>138</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6503,7 +6519,7 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>20</v>
+        <v>321</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>20</v>
@@ -6514,7 +6530,7 @@
         <v>374</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C42" t="s" s="2">
         <v>375</v>
@@ -6527,7 +6543,7 @@
         <v>78</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>20</v>
@@ -6596,7 +6612,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6628,9 +6644,11 @@
         <v>379</v>
       </c>
       <c r="B43" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6648,21 +6666,19 @@
         <v>20</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>109</v>
+        <v>381</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>383</v>
-      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>20</v>
       </c>
@@ -6674,7 +6690,7 @@
         <v>20</v>
       </c>
       <c r="T43" t="s" s="2">
-        <v>384</v>
+        <v>20</v>
       </c>
       <c r="U43" t="s" s="2">
         <v>20</v>
@@ -6686,13 +6702,13 @@
         <v>20</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>179</v>
+        <v>20</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>385</v>
+        <v>20</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>386</v>
+        <v>20</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>20</v>
@@ -6710,28 +6726,28 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>387</v>
+        <v>325</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>101</v>
+        <v>140</v>
       </c>
       <c r="AK43" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>388</v>
+        <v>20</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>389</v>
+        <v>20</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>20</v>
@@ -6739,10 +6755,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>390</v>
+        <v>384</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>391</v>
+        <v>385</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6768,14 +6784,14 @@
         <v>109</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -6788,7 +6804,7 @@
         <v>20</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>20</v>
@@ -6800,13 +6816,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>113</v>
+        <v>179</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>114</v>
+        <v>390</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -6824,7 +6840,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6842,10 +6858,10 @@
         <v>20</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>20</v>
+        <v>393</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>20</v>
@@ -6853,10 +6869,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6867,7 +6883,7 @@
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>20</v>
@@ -6876,22 +6892,20 @@
         <v>20</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>401</v>
+        <v>109</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>404</v>
-      </c>
+        <v>398</v>
+      </c>
+      <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>20</v>
@@ -6904,7 +6918,7 @@
         <v>20</v>
       </c>
       <c r="T45" t="s" s="2">
-        <v>20</v>
+        <v>400</v>
       </c>
       <c r="U45" t="s" s="2">
         <v>20</v>
@@ -6916,13 +6930,13 @@
         <v>20</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>20</v>
+        <v>113</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>20</v>
+        <v>401</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>20</v>
@@ -6940,7 +6954,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6958,10 +6972,10 @@
         <v>20</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>407</v>
+        <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>20</v>
@@ -6969,10 +6983,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6980,10 +6994,10 @@
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>20</v>
@@ -6992,22 +7006,22 @@
         <v>20</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>90</v>
+        <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>20</v>
@@ -7020,7 +7034,7 @@
         <v>20</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>416</v>
+        <v>20</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>20</v>
@@ -7056,7 +7070,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>417</v>
+        <v>411</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7074,10 +7088,10 @@
         <v>20</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>418</v>
+        <v>412</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>419</v>
+        <v>413</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>20</v>
@@ -7085,10 +7099,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>420</v>
+        <v>414</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>421</v>
+        <v>415</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7096,7 +7110,7 @@
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G47" t="s" s="2">
         <v>89</v>
@@ -7111,19 +7125,19 @@
         <v>90</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>422</v>
+        <v>416</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>423</v>
+        <v>417</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>424</v>
+        <v>418</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>425</v>
+        <v>419</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7136,7 +7150,7 @@
         <v>20</v>
       </c>
       <c r="T47" t="s" s="2">
-        <v>20</v>
+        <v>421</v>
       </c>
       <c r="U47" t="s" s="2">
         <v>20</v>
@@ -7172,7 +7186,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7190,10 +7204,10 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>20</v>
+        <v>423</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>20</v>
@@ -7201,10 +7215,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7227,19 +7241,19 @@
         <v>90</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>401</v>
+        <v>427</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="M48" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="O48" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7288,7 +7302,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7309,7 +7323,7 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>20</v>
@@ -7317,10 +7331,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7328,7 +7342,7 @@
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
         <v>89</v>
@@ -7343,17 +7357,19 @@
         <v>90</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>312</v>
+        <v>406</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="M49" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="O49" t="s" s="2">
         <v>439</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>440</v>
-      </c>
-      <c r="N49" s="2"/>
-      <c r="O49" t="s" s="2">
-        <v>441</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7363,10 +7379,10 @@
         <v>20</v>
       </c>
       <c r="S49" t="s" s="2">
-        <v>442</v>
+        <v>20</v>
       </c>
       <c r="T49" t="s" s="2">
-        <v>443</v>
+        <v>20</v>
       </c>
       <c r="U49" t="s" s="2">
         <v>20</v>
@@ -7402,7 +7418,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7423,7 +7439,7 @@
         <v>20</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>20</v>
@@ -7431,10 +7447,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7442,7 +7458,7 @@
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="G50" t="s" s="2">
         <v>89</v>
@@ -7457,17 +7473,17 @@
         <v>90</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>448</v>
+        <v>317</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>20</v>
@@ -7477,10 +7493,10 @@
         <v>20</v>
       </c>
       <c r="S50" t="s" s="2">
-        <v>20</v>
+        <v>447</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>20</v>
+        <v>448</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>20</v>
@@ -7516,7 +7532,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7537,14 +7553,128 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>428</v>
+        <v>450</v>
       </c>
       <c r="AN50" t="s" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="51" hidden="true">
+      <c r="A51" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="B51" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="C51" s="2"/>
+      <c r="D51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="E51" s="2"/>
+      <c r="F51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>90</v>
+      </c>
+      <c r="K51" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="L51" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="P51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q51" s="2"/>
+      <c r="R51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Y51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF51" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AG51" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH51" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AI51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AJ51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="AK51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AM51" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>20</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN50">
+  <autoFilter ref="A1:AN51">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7554,7 +7684,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI49">
+  <conditionalFormatting sqref="A2:AI50">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T16:34:23+05:30</t>
+    <t>2026-06-29T17:18:47+05:30</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
+++ b/314e-ig/output/StructureDefinition-diagnosticreport-notereport-314e.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T17:18:47+05:30</t>
+    <t>2026-07-01T18:18:44+05:30</t>
   </si>
   <si>
     <t>Publisher</t>
